--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.72626339607782</v>
+        <v>2.555517801862646</v>
       </c>
       <c r="D2" t="n">
-        <v>17.12814067557563</v>
+        <v>2.78332285978104</v>
       </c>
       <c r="E2" t="n">
-        <v>12.58100005769797</v>
+        <v>2.04441250937592</v>
       </c>
       <c r="F2" t="n">
-        <v>13.083159690027</v>
+        <v>2.126013449629387</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.620083263446878</v>
+        <v>0.7507635303101177</v>
       </c>
       <c r="D3" t="n">
-        <v>4.500394994039699</v>
+        <v>0.7313141865314511</v>
       </c>
       <c r="E3" t="n">
-        <v>12.58100005769797</v>
+        <v>2.04441250937592</v>
       </c>
       <c r="F3" t="n">
-        <v>13.083159690027</v>
+        <v>2.126013449629387</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.25460164621236</v>
+        <v>2.478872767509509</v>
       </c>
       <c r="D4" t="n">
-        <v>15.43188683190801</v>
+        <v>2.507681610185052</v>
       </c>
       <c r="E4" t="n">
-        <v>12.58100005769797</v>
+        <v>2.04441250937592</v>
       </c>
       <c r="F4" t="n">
-        <v>13.083159690027</v>
+        <v>2.126013449629387</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.62935185234451</v>
+        <v>7.089769676005982</v>
       </c>
       <c r="D5" t="n">
-        <v>44.04113215693434</v>
+        <v>7.156683975501831</v>
       </c>
       <c r="E5" t="n">
-        <v>12.58100005769797</v>
+        <v>2.04441250937592</v>
       </c>
       <c r="F5" t="n">
-        <v>13.083159690027</v>
+        <v>2.126013449629387</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.22256924734584</v>
+        <v>5.723667502693699</v>
       </c>
       <c r="D6" t="n">
-        <v>35.37410326549445</v>
+        <v>5.748291780642849</v>
       </c>
       <c r="E6" t="n">
-        <v>12.58100005769797</v>
+        <v>2.04441250937592</v>
       </c>
       <c r="F6" t="n">
-        <v>13.083159690027</v>
+        <v>2.126013449629387</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.467254393265659</v>
+        <v>1.53842883890567</v>
       </c>
       <c r="D7" t="n">
-        <v>8.853075646325099</v>
+        <v>1.438624792527829</v>
       </c>
       <c r="E7" t="n">
-        <v>12.58100005769797</v>
+        <v>2.04441250937592</v>
       </c>
       <c r="F7" t="n">
-        <v>13.083159690027</v>
+        <v>2.126013449629387</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.99624563538974</v>
+        <v>5.199389915750833</v>
       </c>
       <c r="D8" t="n">
-        <v>32.38309234686478</v>
+        <v>5.262252506365527</v>
       </c>
       <c r="E8" t="n">
-        <v>12.58100005769797</v>
+        <v>2.04441250937592</v>
       </c>
       <c r="F8" t="n">
-        <v>13.083159690027</v>
+        <v>2.126013449629387</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.22810699202232</v>
+        <v>4.424567386203626</v>
       </c>
       <c r="D9" t="n">
-        <v>27.34802753036542</v>
+        <v>4.444054473684382</v>
       </c>
       <c r="E9" t="n">
-        <v>12.58100005769797</v>
+        <v>2.04441250937592</v>
       </c>
       <c r="F9" t="n">
-        <v>13.083159690027</v>
+        <v>2.126013449629387</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59674660380064</v>
+        <v>5.296971323117604</v>
       </c>
       <c r="D10" t="n">
-        <v>34.94992581258936</v>
+        <v>5.679362944545771</v>
       </c>
       <c r="E10" t="n">
-        <v>12.58100005769797</v>
+        <v>2.04441250937592</v>
       </c>
       <c r="F10" t="n">
-        <v>13.083159690027</v>
+        <v>2.126013449629387</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.33310469700466</v>
+        <v>2.654129513263257</v>
       </c>
       <c r="D11" t="n">
-        <v>15.92265117488471</v>
+        <v>2.587430815918765</v>
       </c>
       <c r="E11" t="n">
-        <v>12.58100005769797</v>
+        <v>2.04441250937592</v>
       </c>
       <c r="F11" t="n">
-        <v>13.083159690027</v>
+        <v>2.126013449629387</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.51011071737555</v>
+        <v>7.395392991573527</v>
       </c>
       <c r="D12" t="n">
-        <v>47.47639636482971</v>
+        <v>7.714914409284829</v>
       </c>
       <c r="E12" t="n">
-        <v>12.58100005769797</v>
+        <v>2.04441250937592</v>
       </c>
       <c r="F12" t="n">
-        <v>13.083159690027</v>
+        <v>2.126013449629387</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>27.17437554668787</v>
+        <v>4.415836026336779</v>
       </c>
       <c r="D13" t="n">
-        <v>28.93025893086211</v>
+        <v>4.701167076265094</v>
       </c>
       <c r="E13" t="n">
-        <v>12.58100005769797</v>
+        <v>2.04441250937592</v>
       </c>
       <c r="F13" t="n">
-        <v>13.083159690027</v>
+        <v>2.126013449629387</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
